--- a/medical_application_forms/039_medical_liability_waiver_form--medical_application_forms.xlsx
+++ b/medical_application_forms/039_medical_liability_waiver_form--medical_application_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -510,15 +510,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>medical_liability_waiver_form_1</t>
+          <t>participant_details</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>participant_details</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Participant Details</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide your contact information and medical history</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -533,15 +537,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>participant_details</t>
+          <t>waiver_information</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>participant_details</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Waiver Information</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please review and sign the waiver</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -556,15 +564,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>participant_details_2</t>
+          <t>emergency_contact</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>participant_details_2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Emergency Contact</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide emergency contact information</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -579,15 +591,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>medical_liability_waiver_form_4</t>
+          <t>insurance_info</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>participant_details_3</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Insurance Information</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please provide insurance information</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -602,15 +618,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>medical_liability_waiver_form_5</t>
+          <t>medical_info</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>participant_details_4</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Medical Information</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide medical information</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -625,15 +645,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>medical_liability_waiver_form_6</t>
+          <t>acknowledgement</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>participant_details_5</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Acknowledgement</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please acknowledge form completion</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -648,15 +672,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medical_liability_waiver_form_7</t>
+          <t>additional_medical_info</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>participant_details_6</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Additional Medical Information</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please provide additional medical information</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -671,15 +699,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>medical_liability_waiver_form_8</t>
+          <t>acknowledgement_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>participant_details_7</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Acknowledgement 2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please acknowledge form completion</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -694,39 +726,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>participant_details_8</t>
+          <t>medical_liability_waiver_form_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>participant_details</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Medical Liability Waiver</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please review and sign the waiver</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>participant_details_9</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>participant_details_2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
